--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="38">
   <si>
     <t>configuracion</t>
   </si>
@@ -570,7 +570,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -582,11 +582,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
       </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L2" t="s">
         <v>34</v>
       </c>
@@ -603,7 +609,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -615,7 +621,7 @@
         <v>7</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -635,7 +641,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -647,11 +653,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L3" t="s">
         <v>34</v>
       </c>
@@ -668,7 +680,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -680,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V3">
         <v>7</v>
@@ -712,11 +724,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L4" t="s">
         <v>32</v>
       </c>
@@ -733,7 +751,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -777,10 +795,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L5" t="s">
         <v>33</v>
@@ -842,10 +866,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L6" t="s">
         <v>34</v>
@@ -907,10 +937,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L7" t="s">
         <v>34</v>
@@ -972,11 +1008,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
       </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L8" t="s">
         <v>34</v>
       </c>
@@ -993,7 +1035,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -1037,11 +1079,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
       <c r="L9" t="s">
         <v>34</v>
       </c>
@@ -1070,7 +1118,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1102,10 +1150,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L10" t="s">
         <v>34</v>
@@ -1167,10 +1221,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L11" t="s">
         <v>34</v>
@@ -1232,11 +1292,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
+      <c r="J12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
       <c r="L12" t="s">
         <v>34</v>
       </c>
@@ -1265,7 +1331,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1297,10 +1363,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L13" t="s">
         <v>31</v>
@@ -1350,7 +1422,7 @@
         <v>25</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1362,11 +1434,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L14" t="s">
         <v>34</v>
       </c>
@@ -1383,7 +1461,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
@@ -1395,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1427,11 +1505,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
+      <c r="J15" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L15" t="s">
         <v>35</v>
       </c>
@@ -1448,7 +1532,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -1492,10 +1576,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L16" t="s">
         <v>34</v>
@@ -1557,10 +1647,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L17" t="s">
         <v>34</v>
@@ -1622,10 +1718,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L18" t="s">
         <v>34</v>
@@ -1687,10 +1789,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H19">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L19" t="s">
         <v>34</v>
@@ -1752,10 +1860,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H20">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L20" t="s">
         <v>34</v>
@@ -1817,10 +1931,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H21">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L21" t="s">
         <v>37</v>
@@ -1882,10 +2002,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L22" t="s">
         <v>37</v>
@@ -1947,11 +2073,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
       </c>
+      <c r="J23" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
       <c r="L23" t="s">
         <v>34</v>
       </c>
@@ -1980,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2012,10 +2144,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L24" t="s">
         <v>34</v>
@@ -2077,10 +2215,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L25" t="s">
         <v>34</v>
@@ -2130,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="D26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2142,11 +2286,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
       </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L26" t="s">
         <v>34</v>
       </c>
@@ -2163,7 +2313,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="b">
         <v>1</v>
@@ -2175,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2207,11 +2357,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H27">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
       </c>
+      <c r="J27" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
       <c r="L27" t="s">
         <v>34</v>
       </c>
@@ -2240,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2260,7 +2416,7 @@
         <v>25</v>
       </c>
       <c r="D28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2272,11 +2428,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
       </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L28" t="s">
         <v>34</v>
       </c>
@@ -2293,7 +2455,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
@@ -2305,7 +2467,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2325,7 +2487,7 @@
         <v>25</v>
       </c>
       <c r="D29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -2337,11 +2499,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
       </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L29" t="s">
         <v>34</v>
       </c>
@@ -2358,7 +2526,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="b">
         <v>1</v>
@@ -2370,7 +2538,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2402,10 +2570,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H30">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L30" t="s">
         <v>34</v>
@@ -2455,7 +2629,7 @@
         <v>25</v>
       </c>
       <c r="D31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -2467,11 +2641,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H31">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
       </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L31" t="s">
         <v>34</v>
       </c>
@@ -2488,7 +2668,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
@@ -2500,7 +2680,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2532,11 +2712,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H32">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
       </c>
+      <c r="J32" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
       <c r="L32" t="s">
         <v>34</v>
       </c>
@@ -2565,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2597,11 +2783,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
       </c>
+      <c r="J33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
       <c r="L33" t="s">
         <v>34</v>
       </c>
@@ -2630,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -2650,7 +2842,7 @@
         <v>25</v>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -2662,11 +2854,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
       </c>
+      <c r="J34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L34" t="s">
         <v>34</v>
       </c>
@@ -2683,7 +2881,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
@@ -2695,7 +2893,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -2715,7 +2913,7 @@
         <v>25</v>
       </c>
       <c r="D35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -2727,11 +2925,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H35">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
       </c>
+      <c r="J35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L35" t="s">
         <v>34</v>
       </c>
@@ -2748,7 +2952,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
@@ -2760,7 +2964,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -2792,11 +2996,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H36">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
       </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L36" t="s">
         <v>37</v>
       </c>
@@ -2813,7 +3023,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
@@ -2857,10 +3067,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H37">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L37" t="s">
         <v>34</v>
@@ -2922,11 +3138,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H38">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
       </c>
+      <c r="J38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L38" t="s">
         <v>37</v>
       </c>
@@ -2943,7 +3165,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
@@ -2987,11 +3209,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H39">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
       </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L39" t="s">
         <v>32</v>
       </c>
@@ -3008,7 +3236,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -3052,11 +3280,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
       </c>
+      <c r="J40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L40" t="s">
         <v>35</v>
       </c>
@@ -3073,7 +3307,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -3117,10 +3351,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H41">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L41" t="s">
         <v>34</v>
@@ -3182,10 +3422,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H42">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L42" t="s">
         <v>33</v>
@@ -3247,10 +3493,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H43">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L43" t="s">
         <v>34</v>
@@ -3312,10 +3564,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H44">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L44" t="s">
         <v>37</v>
@@ -3377,10 +3635,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H45">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L45" t="s">
         <v>33</v>
@@ -3442,11 +3706,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H46">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
       </c>
+      <c r="J46" t="s">
+        <v>37</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
       <c r="L46" t="s">
         <v>34</v>
       </c>
@@ -3463,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="b">
         <v>1</v>
@@ -3495,7 +3765,7 @@
         <v>25</v>
       </c>
       <c r="D47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>7</v>
@@ -3507,11 +3777,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H47">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
       </c>
+      <c r="J47" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
       <c r="L47" t="s">
         <v>34</v>
       </c>
@@ -3528,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="b">
         <v>1</v>
@@ -3560,7 +3836,7 @@
         <v>25</v>
       </c>
       <c r="D48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <v>7</v>
@@ -3572,11 +3848,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
       </c>
+      <c r="J48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L48" t="s">
         <v>30</v>
       </c>
@@ -3593,7 +3875,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="b">
         <v>1</v>
@@ -3605,7 +3887,7 @@
         <v>6</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V48">
         <v>6</v>
@@ -3637,10 +3919,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H49">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L49" t="s">
         <v>34</v>
@@ -3702,11 +3990,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
       </c>
+      <c r="J50" t="s">
+        <v>34</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
       <c r="L50" t="s">
         <v>30</v>
       </c>
@@ -3735,7 +4029,7 @@
         <v>6</v>
       </c>
       <c r="U50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V50">
         <v>6</v>
@@ -3767,10 +4061,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H51">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L51" t="s">
         <v>34</v>
@@ -3832,10 +4132,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H52">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
       </c>
       <c r="L52" t="s">
         <v>31</v>
@@ -3897,11 +4203,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H53">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
       </c>
+      <c r="J53" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
       <c r="L53" t="s">
         <v>34</v>
       </c>
@@ -3930,7 +4242,7 @@
         <v>7</v>
       </c>
       <c r="U53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V53">
         <v>7</v>
@@ -3962,10 +4274,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L54" t="s">
         <v>34</v>
@@ -4027,11 +4345,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
       </c>
+      <c r="J55" t="s">
+        <v>33</v>
+      </c>
+      <c r="K55">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L55" t="s">
         <v>34</v>
       </c>
@@ -4048,7 +4372,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
@@ -4092,11 +4416,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H56">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
       </c>
+      <c r="J56" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
       <c r="L56" t="s">
         <v>34</v>
       </c>
@@ -4125,7 +4455,7 @@
         <v>7</v>
       </c>
       <c r="U56">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V56">
         <v>7</v>
@@ -4157,10 +4487,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H57">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>32</v>
+      </c>
+      <c r="K57">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L57" t="s">
         <v>34</v>
@@ -4222,10 +4558,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H58">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L58" t="s">
         <v>34</v>
@@ -4287,10 +4629,16 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H59">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L59" t="s">
         <v>34</v>
@@ -4352,11 +4700,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
       </c>
+      <c r="J60" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L60" t="s">
         <v>33</v>
       </c>
@@ -4373,7 +4727,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4417,11 +4771,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H61">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>33</v>
+      </c>
+      <c r="K61">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L61" t="s">
         <v>37</v>
       </c>
@@ -4438,7 +4798,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -4482,11 +4842,17 @@
         <v>0.5671660693915587</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
       </c>
+      <c r="J62" t="s">
+        <v>34</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
       <c r="L62" t="s">
         <v>34</v>
       </c>
@@ -4515,7 +4881,7 @@
         <v>7</v>
       </c>
       <c r="U62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V62">
         <v>7</v>
@@ -4547,10 +4913,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H63">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L63" t="s">
         <v>33</v>
@@ -4612,10 +4984,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H64">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L64" t="s">
         <v>33</v>
@@ -4677,11 +5055,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
       </c>
+      <c r="J65" t="s">
+        <v>37</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
       <c r="L65" t="s">
         <v>37</v>
       </c>
@@ -4698,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
@@ -4742,11 +5126,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
       </c>
+      <c r="J66" t="s">
+        <v>37</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
       <c r="L66" t="s">
         <v>34</v>
       </c>
@@ -4763,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="b">
         <v>1</v>
@@ -4807,10 +5197,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H67">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L67" t="s">
         <v>34</v>
@@ -4872,10 +5268,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>35</v>
+      </c>
+      <c r="K68">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L68" t="s">
         <v>32</v>
@@ -4925,7 +5327,7 @@
         <v>26</v>
       </c>
       <c r="D69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69">
         <v>7</v>
@@ -4937,11 +5339,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H69">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
+      <c r="J69" t="s">
+        <v>33</v>
+      </c>
+      <c r="K69">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L69" t="s">
         <v>34</v>
       </c>
@@ -4958,7 +5366,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -4970,7 +5378,7 @@
         <v>7</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V69">
         <v>7</v>
@@ -5002,10 +5410,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H70">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
+      </c>
+      <c r="J70" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L70" t="s">
         <v>35</v>
@@ -5067,10 +5481,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H71">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>32</v>
+      </c>
+      <c r="K71">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L71" t="s">
         <v>31</v>
@@ -5132,10 +5552,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
+      </c>
+      <c r="J72" t="s">
+        <v>32</v>
+      </c>
+      <c r="K72">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L72" t="s">
         <v>36</v>
@@ -5197,10 +5623,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H73">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
+      </c>
+      <c r="J73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K73">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L73" t="s">
         <v>34</v>
@@ -5262,10 +5694,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H74">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L74" t="s">
         <v>34</v>
@@ -5327,10 +5765,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H75">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L75" t="s">
         <v>34</v>
@@ -5380,7 +5824,7 @@
         <v>26</v>
       </c>
       <c r="D76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>7</v>
@@ -5392,11 +5836,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H76">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
+      <c r="J76" t="s">
+        <v>30</v>
+      </c>
+      <c r="K76">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L76" t="s">
         <v>34</v>
       </c>
@@ -5413,7 +5863,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -5425,7 +5875,7 @@
         <v>7</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -5445,7 +5895,7 @@
         <v>26</v>
       </c>
       <c r="D77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>7</v>
@@ -5457,11 +5907,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
       </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L77" t="s">
         <v>34</v>
       </c>
@@ -5478,7 +5934,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -5490,7 +5946,7 @@
         <v>7</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V77">
         <v>7</v>
@@ -5522,11 +5978,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
       </c>
+      <c r="J78" t="s">
+        <v>30</v>
+      </c>
+      <c r="K78">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L78" t="s">
         <v>32</v>
       </c>
@@ -5543,7 +6005,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
@@ -5587,10 +6049,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H79">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>35</v>
+      </c>
+      <c r="K79">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L79" t="s">
         <v>34</v>
@@ -5652,10 +6120,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H80">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L80" t="s">
         <v>34</v>
@@ -5717,10 +6191,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H81">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>31</v>
+      </c>
+      <c r="K81">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L81" t="s">
         <v>34</v>
@@ -5770,7 +6250,7 @@
         <v>26</v>
       </c>
       <c r="D82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>7</v>
@@ -5782,11 +6262,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
       </c>
+      <c r="J82" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L82" t="s">
         <v>34</v>
       </c>
@@ -5803,7 +6289,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -5815,7 +6301,7 @@
         <v>7</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V82">
         <v>7</v>
@@ -5847,10 +6333,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H83">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>35</v>
+      </c>
+      <c r="K83">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L83" t="s">
         <v>32</v>
@@ -5912,10 +6404,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>32</v>
+      </c>
+      <c r="K84">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L84" t="s">
         <v>34</v>
@@ -5977,11 +6475,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H85">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
       </c>
+      <c r="J85" t="s">
+        <v>37</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
       <c r="L85" t="s">
         <v>34</v>
       </c>
@@ -5998,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -6042,10 +6546,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H86">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>35</v>
+      </c>
+      <c r="K86">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L86" t="s">
         <v>34</v>
@@ -6107,11 +6617,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
       </c>
+      <c r="J87" t="s">
+        <v>37</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
       <c r="L87" t="s">
         <v>34</v>
       </c>
@@ -6128,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -6172,11 +6688,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H88">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
       </c>
+      <c r="J88" t="s">
+        <v>33</v>
+      </c>
+      <c r="K88">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L88" t="s">
         <v>34</v>
       </c>
@@ -6193,7 +6715,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -6225,7 +6747,7 @@
         <v>26</v>
       </c>
       <c r="D89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89">
         <v>7</v>
@@ -6237,11 +6759,17 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H89">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
       </c>
+      <c r="J89" t="s">
+        <v>30</v>
+      </c>
+      <c r="K89">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L89" t="s">
         <v>34</v>
       </c>
@@ -6258,7 +6786,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -6270,7 +6798,7 @@
         <v>7</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V89">
         <v>7</v>
@@ -6302,10 +6830,16 @@
         <v>0.5994042617493563</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0.8088310105697705</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>32</v>
+      </c>
+      <c r="K90">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L90" t="s">
         <v>32</v>
@@ -6355,7 +6889,7 @@
         <v>27</v>
       </c>
       <c r="D91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91">
         <v>7</v>
@@ -6367,11 +6901,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
       </c>
+      <c r="J91" t="s">
+        <v>30</v>
+      </c>
+      <c r="K91">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L91" t="s">
         <v>30</v>
       </c>
@@ -6388,7 +6928,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -6400,7 +6940,7 @@
         <v>6</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V91">
         <v>6</v>
@@ -6432,11 +6972,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
       </c>
+      <c r="J92" t="s">
+        <v>34</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
       <c r="L92" t="s">
         <v>34</v>
       </c>
@@ -6465,7 +7011,7 @@
         <v>7</v>
       </c>
       <c r="U92">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="V92">
         <v>7</v>
@@ -6485,7 +7031,7 @@
         <v>27</v>
       </c>
       <c r="D93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93">
         <v>7</v>
@@ -6497,11 +7043,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
       </c>
+      <c r="J93" t="s">
+        <v>30</v>
+      </c>
+      <c r="K93">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L93" t="s">
         <v>34</v>
       </c>
@@ -6518,7 +7070,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -6530,7 +7082,7 @@
         <v>7</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V93">
         <v>7</v>
@@ -6550,7 +7102,7 @@
         <v>27</v>
       </c>
       <c r="D94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94">
         <v>7</v>
@@ -6562,11 +7114,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H94">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
       </c>
+      <c r="J94" t="s">
+        <v>30</v>
+      </c>
+      <c r="K94">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L94" t="s">
         <v>30</v>
       </c>
@@ -6583,7 +7141,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -6595,7 +7153,7 @@
         <v>6</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V94">
         <v>6</v>
@@ -6627,11 +7185,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H95">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
       </c>
+      <c r="J95" t="s">
+        <v>37</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
       <c r="L95" t="s">
         <v>34</v>
       </c>
@@ -6648,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -6692,11 +7256,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H96">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
       </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L96" t="s">
         <v>31</v>
       </c>
@@ -6713,7 +7283,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
@@ -6757,10 +7327,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L97" t="s">
         <v>34</v>
@@ -6822,10 +7398,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
+      </c>
+      <c r="J98" t="s">
+        <v>34</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
       </c>
       <c r="L98" t="s">
         <v>31</v>
@@ -6887,10 +7469,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H99">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
+      </c>
+      <c r="J99" t="s">
+        <v>32</v>
+      </c>
+      <c r="K99">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L99" t="s">
         <v>31</v>
@@ -6952,10 +7540,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
+      </c>
+      <c r="J100" t="s">
+        <v>32</v>
+      </c>
+      <c r="K100">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L100" t="s">
         <v>34</v>
@@ -7017,11 +7611,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H101">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
       </c>
+      <c r="J101" t="s">
+        <v>30</v>
+      </c>
+      <c r="K101">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L101" t="s">
         <v>35</v>
       </c>
@@ -7038,7 +7638,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
@@ -7082,10 +7682,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
+      </c>
+      <c r="J102" t="s">
+        <v>31</v>
+      </c>
+      <c r="K102">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L102" t="s">
         <v>34</v>
@@ -7147,11 +7753,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H103">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
       </c>
+      <c r="J103" t="s">
+        <v>34</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
       <c r="L103" t="s">
         <v>30</v>
       </c>
@@ -7180,7 +7792,7 @@
         <v>6</v>
       </c>
       <c r="U103">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="V103">
         <v>6</v>
@@ -7212,11 +7824,17 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
       </c>
+      <c r="J104" t="s">
+        <v>33</v>
+      </c>
+      <c r="K104">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L104" t="s">
         <v>35</v>
       </c>
@@ -7233,7 +7851,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="b">
         <v>0</v>
@@ -7277,10 +7895,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H105">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
+      </c>
+      <c r="J105" t="s">
+        <v>31</v>
+      </c>
+      <c r="K105">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L105" t="s">
         <v>34</v>
@@ -7342,10 +7966,16 @@
         <v>0.8030460197800602</v>
       </c>
       <c r="H106">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
+      </c>
+      <c r="J106" t="s">
+        <v>34</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
       </c>
       <c r="L106" t="s">
         <v>31</v>
@@ -7407,11 +8037,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H107">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
       </c>
+      <c r="J107" t="s">
+        <v>34</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
       <c r="L107" t="s">
         <v>34</v>
       </c>
@@ -7440,7 +8076,7 @@
         <v>7</v>
       </c>
       <c r="U107">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V107">
         <v>7</v>
@@ -7472,10 +8108,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H108">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I108" t="s">
         <v>15</v>
+      </c>
+      <c r="J108" t="s">
+        <v>36</v>
+      </c>
+      <c r="K108">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L108" t="s">
         <v>31</v>
@@ -7537,10 +8179,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H109">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
+      </c>
+      <c r="J109" t="s">
+        <v>31</v>
+      </c>
+      <c r="K109">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L109" t="s">
         <v>34</v>
@@ -7602,10 +8250,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H110">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
+      </c>
+      <c r="J110" t="s">
+        <v>30</v>
+      </c>
+      <c r="K110">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L110" t="s">
         <v>34</v>
@@ -7667,10 +8321,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H111">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
+      </c>
+      <c r="J111" t="s">
+        <v>34</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
       </c>
       <c r="L111" t="s">
         <v>34</v>
@@ -7732,10 +8392,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H112">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I112" t="s">
         <v>15</v>
+      </c>
+      <c r="J112" t="s">
+        <v>32</v>
+      </c>
+      <c r="K112">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L112" t="s">
         <v>34</v>
@@ -7797,10 +8463,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H113">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I113" t="s">
         <v>15</v>
+      </c>
+      <c r="J113" t="s">
+        <v>34</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
       </c>
       <c r="L113" t="s">
         <v>37</v>
@@ -7862,11 +8534,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H114">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
       </c>
+      <c r="J114" t="s">
+        <v>34</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
       <c r="L114" t="s">
         <v>34</v>
       </c>
@@ -7895,7 +8573,7 @@
         <v>7</v>
       </c>
       <c r="U114">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V114">
         <v>7</v>
@@ -7915,7 +8593,7 @@
         <v>28</v>
       </c>
       <c r="D115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>7</v>
@@ -7927,11 +8605,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H115">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I115" t="s">
         <v>15</v>
       </c>
+      <c r="J115" t="s">
+        <v>37</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
       <c r="L115" t="s">
         <v>34</v>
       </c>
@@ -7948,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="Q115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="b">
         <v>1</v>
@@ -7992,10 +8676,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
+      </c>
+      <c r="J116" t="s">
+        <v>31</v>
+      </c>
+      <c r="K116">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L116" t="s">
         <v>32</v>
@@ -8057,10 +8747,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H117">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="s">
         <v>15</v>
+      </c>
+      <c r="J117" t="s">
+        <v>30</v>
+      </c>
+      <c r="K117">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L117" t="s">
         <v>34</v>
@@ -8122,10 +8818,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H118">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I118" t="s">
         <v>15</v>
+      </c>
+      <c r="J118" t="s">
+        <v>30</v>
+      </c>
+      <c r="K118">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L118" t="s">
         <v>34</v>
@@ -8187,10 +8889,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H119">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
+      </c>
+      <c r="J119" t="s">
+        <v>32</v>
+      </c>
+      <c r="K119">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L119" t="s">
         <v>32</v>
@@ -8252,10 +8960,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H120">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
+      </c>
+      <c r="J120" t="s">
+        <v>34</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
       </c>
       <c r="L120" t="s">
         <v>36</v>
@@ -8317,10 +9031,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H121">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I121" t="s">
         <v>15</v>
+      </c>
+      <c r="J121" t="s">
+        <v>34</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
       </c>
       <c r="L121" t="s">
         <v>33</v>
@@ -8382,10 +9102,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H122">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="s">
         <v>15</v>
+      </c>
+      <c r="J122" t="s">
+        <v>34</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
       </c>
       <c r="L122" t="s">
         <v>36</v>
@@ -8447,10 +9173,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H123">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I123" t="s">
         <v>15</v>
+      </c>
+      <c r="J123" t="s">
+        <v>32</v>
+      </c>
+      <c r="K123">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L123" t="s">
         <v>34</v>
@@ -8512,10 +9244,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H124">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I124" t="s">
         <v>15</v>
+      </c>
+      <c r="J124" t="s">
+        <v>32</v>
+      </c>
+      <c r="K124">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L124" t="s">
         <v>34</v>
@@ -8577,10 +9315,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H125">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I125" t="s">
         <v>15</v>
+      </c>
+      <c r="J125" t="s">
+        <v>34</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
       </c>
       <c r="L125" t="s">
         <v>35</v>
@@ -8642,10 +9386,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H126">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I126" t="s">
         <v>15</v>
+      </c>
+      <c r="J126" t="s">
+        <v>30</v>
+      </c>
+      <c r="K126">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L126" t="s">
         <v>34</v>
@@ -8707,10 +9457,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H127">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
+      </c>
+      <c r="J127" t="s">
+        <v>35</v>
+      </c>
+      <c r="K127">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L127" t="s">
         <v>37</v>
@@ -8772,10 +9528,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H128">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="s">
         <v>15</v>
+      </c>
+      <c r="J128" t="s">
+        <v>32</v>
+      </c>
+      <c r="K128">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L128" t="s">
         <v>34</v>
@@ -8837,10 +9599,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H129">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I129" t="s">
         <v>15</v>
+      </c>
+      <c r="J129" t="s">
+        <v>34</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
       </c>
       <c r="L129" t="s">
         <v>34</v>
@@ -8902,10 +9670,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H130">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="s">
         <v>15</v>
+      </c>
+      <c r="J130" t="s">
+        <v>35</v>
+      </c>
+      <c r="K130">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L130" t="s">
         <v>34</v>
@@ -8967,10 +9741,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H131">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="s">
         <v>15</v>
+      </c>
+      <c r="J131" t="s">
+        <v>31</v>
+      </c>
+      <c r="K131">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L131" t="s">
         <v>32</v>
@@ -9032,10 +9812,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H132">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I132" t="s">
         <v>15</v>
+      </c>
+      <c r="J132" t="s">
+        <v>34</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
       </c>
       <c r="L132" t="s">
         <v>34</v>
@@ -9097,10 +9883,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H133">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I133" t="s">
         <v>15</v>
+      </c>
+      <c r="J133" t="s">
+        <v>30</v>
+      </c>
+      <c r="K133">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L133" t="s">
         <v>30</v>
@@ -9162,10 +9954,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H134">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I134" t="s">
         <v>15</v>
+      </c>
+      <c r="J134" t="s">
+        <v>30</v>
+      </c>
+      <c r="K134">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L134" t="s">
         <v>34</v>
@@ -9227,10 +10025,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H135">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I135" t="s">
         <v>15</v>
+      </c>
+      <c r="J135" t="s">
+        <v>34</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
@@ -9292,10 +10096,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H136">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I136" t="s">
         <v>15</v>
+      </c>
+      <c r="J136" t="s">
+        <v>32</v>
+      </c>
+      <c r="K136">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L136" t="s">
         <v>34</v>
@@ -9357,11 +10167,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H137">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I137" t="s">
         <v>15</v>
       </c>
+      <c r="J137" t="s">
+        <v>34</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
       <c r="L137" t="s">
         <v>34</v>
       </c>
@@ -9390,7 +10206,7 @@
         <v>7</v>
       </c>
       <c r="U137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V137">
         <v>7</v>
@@ -9422,11 +10238,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H138">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
       </c>
+      <c r="J138" t="s">
+        <v>34</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
       <c r="L138" t="s">
         <v>30</v>
       </c>
@@ -9455,7 +10277,7 @@
         <v>6</v>
       </c>
       <c r="U138">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V138">
         <v>6</v>
@@ -9487,10 +10309,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H139">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I139" t="s">
         <v>15</v>
+      </c>
+      <c r="J139" t="s">
+        <v>30</v>
+      </c>
+      <c r="K139">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L139" t="s">
         <v>34</v>
@@ -9552,10 +10380,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H140">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="s">
         <v>15</v>
+      </c>
+      <c r="J140" t="s">
+        <v>33</v>
+      </c>
+      <c r="K140">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L140" t="s">
         <v>34</v>
@@ -9617,10 +10451,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H141">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I141" t="s">
         <v>15</v>
+      </c>
+      <c r="J141" t="s">
+        <v>33</v>
+      </c>
+      <c r="K141">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L141" t="s">
         <v>33</v>
@@ -9682,10 +10522,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H142">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="s">
         <v>15</v>
+      </c>
+      <c r="J142" t="s">
+        <v>33</v>
+      </c>
+      <c r="K142">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L142" t="s">
         <v>32</v>
@@ -9747,10 +10593,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H143">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I143" t="s">
         <v>15</v>
+      </c>
+      <c r="J143" t="s">
+        <v>33</v>
+      </c>
+      <c r="K143">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L143" t="s">
         <v>34</v>
@@ -9812,11 +10664,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H144">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I144" t="s">
         <v>15</v>
       </c>
+      <c r="J144" t="s">
+        <v>34</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
       <c r="L144" t="s">
         <v>34</v>
       </c>
@@ -9845,7 +10703,7 @@
         <v>7</v>
       </c>
       <c r="U144">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V144">
         <v>7</v>
@@ -9877,11 +10735,17 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H145">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I145" t="s">
         <v>15</v>
       </c>
+      <c r="J145" t="s">
+        <v>34</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
       <c r="L145" t="s">
         <v>34</v>
       </c>
@@ -9910,7 +10774,7 @@
         <v>7</v>
       </c>
       <c r="U145">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V145">
         <v>7</v>
@@ -9942,10 +10806,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H146">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I146" t="s">
         <v>15</v>
+      </c>
+      <c r="J146" t="s">
+        <v>34</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
       </c>
       <c r="L146" t="s">
         <v>32</v>
@@ -10007,10 +10877,16 @@
         <v>0.5680099816657718</v>
       </c>
       <c r="H147">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I147" t="s">
         <v>15</v>
+      </c>
+      <c r="J147" t="s">
+        <v>30</v>
+      </c>
+      <c r="K147">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L147" t="s">
         <v>31</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
@@ -621,7 +621,7 @@
         <v>7</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3">
         <v>7</v>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1035,13 +1035,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1118,7 +1118,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1473,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2112,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2325,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2467,7 +2467,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2538,7 +2538,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2680,7 +2680,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2822,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -2893,7 +2893,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -2964,7 +2964,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>25</v>
       </c>
       <c r="D48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>7</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="b">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         <v>6</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V48">
         <v>6</v>
@@ -3978,7 +3978,7 @@
         <v>25</v>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>7</v>
@@ -4020,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         <v>7</v>
       </c>
       <c r="U56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V56">
         <v>7</v>
@@ -4520,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="S57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57">
         <v>7</v>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -4881,7 +4881,7 @@
         <v>7</v>
       </c>
       <c r="U62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62">
         <v>7</v>
@@ -5230,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="S67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67">
         <v>7</v>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68">
         <v>5</v>
@@ -5327,7 +5327,7 @@
         <v>26</v>
       </c>
       <c r="D69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>7</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -5378,7 +5378,7 @@
         <v>7</v>
       </c>
       <c r="U69">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V69">
         <v>7</v>
@@ -5656,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73">
         <v>7</v>
@@ -5875,7 +5875,7 @@
         <v>7</v>
       </c>
       <c r="U76">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -5946,7 +5946,7 @@
         <v>7</v>
       </c>
       <c r="U77">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V77">
         <v>7</v>
@@ -6082,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79">
         <v>7</v>
@@ -6301,7 +6301,7 @@
         <v>7</v>
       </c>
       <c r="U82">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V82">
         <v>7</v>
@@ -6437,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="S84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84">
         <v>7</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="S86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86">
         <v>7</v>
@@ -6715,7 +6715,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -6798,7 +6798,7 @@
         <v>7</v>
       </c>
       <c r="U89">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="V89">
         <v>7</v>
@@ -6889,7 +6889,7 @@
         <v>27</v>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>7</v>
@@ -6931,7 +6931,7 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         <v>6</v>
       </c>
       <c r="U91">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V91">
         <v>6</v>
@@ -6960,7 +6960,7 @@
         <v>27</v>
       </c>
       <c r="D92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>7</v>
@@ -7002,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="b">
         <v>1</v>
@@ -7011,7 +7011,7 @@
         <v>7</v>
       </c>
       <c r="U92">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V92">
         <v>7</v>
@@ -7031,7 +7031,7 @@
         <v>27</v>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>7</v>
@@ -7073,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="b">
         <v>1</v>
@@ -7082,7 +7082,7 @@
         <v>7</v>
       </c>
       <c r="U93">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V93">
         <v>7</v>
@@ -7102,7 +7102,7 @@
         <v>27</v>
       </c>
       <c r="D94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>7</v>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="b">
         <v>1</v>
@@ -7153,7 +7153,7 @@
         <v>6</v>
       </c>
       <c r="U94">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V94">
         <v>6</v>
@@ -7215,7 +7215,7 @@
         <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97">
         <v>7</v>
@@ -7570,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="b">
         <v>1</v>
@@ -7712,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102">
         <v>7</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>7</v>
@@ -7783,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="b">
         <v>1</v>
@@ -7792,7 +7792,7 @@
         <v>6</v>
       </c>
       <c r="U103">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V103">
         <v>6</v>
@@ -7851,13 +7851,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="b">
         <v>0</v>
       </c>
       <c r="S104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104">
         <v>3</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="R105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105">
         <v>7</v>
@@ -8076,7 +8076,7 @@
         <v>7</v>
       </c>
       <c r="U107">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V107">
         <v>7</v>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="S108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108">
         <v>4</v>
@@ -8360,7 +8360,7 @@
         <v>7</v>
       </c>
       <c r="U111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V111">
         <v>7</v>
@@ -8573,7 +8573,7 @@
         <v>7</v>
       </c>
       <c r="U114">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V114">
         <v>7</v>
@@ -9277,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="S124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124">
         <v>7</v>
@@ -9638,7 +9638,7 @@
         <v>7</v>
       </c>
       <c r="U129">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V129">
         <v>7</v>
@@ -9703,7 +9703,7 @@
         <v>1</v>
       </c>
       <c r="S130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T130">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>7</v>
       </c>
       <c r="U132">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V132">
         <v>7</v>
@@ -10064,7 +10064,7 @@
         <v>7</v>
       </c>
       <c r="U135">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V135">
         <v>7</v>
@@ -10129,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="S136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136">
         <v>7</v>
@@ -10206,7 +10206,7 @@
         <v>7</v>
       </c>
       <c r="U137">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V137">
         <v>7</v>
@@ -10277,7 +10277,7 @@
         <v>6</v>
       </c>
       <c r="U138">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V138">
         <v>6</v>
@@ -10703,7 +10703,7 @@
         <v>7</v>
       </c>
       <c r="U144">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V144">
         <v>7</v>
@@ -11046,7 +11046,7 @@
         <v>7</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V149">
         <v>7</v>
@@ -11196,7 +11196,7 @@
         <v>25</v>
       </c>
       <c r="D152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>7</v>
@@ -11235,13 +11235,13 @@
         <v>1</v>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152">
         <v>7</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V152">
         <v>7</v>
@@ -11365,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="S154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154">
         <v>7</v>
@@ -11436,7 +11436,7 @@
         <v>7</v>
       </c>
       <c r="U155">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V155">
         <v>7</v>
@@ -11631,7 +11631,7 @@
         <v>7</v>
       </c>
       <c r="U158">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V158">
         <v>7</v>
@@ -11846,7 +11846,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162">
         <v>7</v>
@@ -11885,13 +11885,13 @@
         <v>1</v>
       </c>
       <c r="S162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T162">
         <v>7</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V162">
         <v>7</v>
@@ -12106,7 +12106,7 @@
         <v>25</v>
       </c>
       <c r="D166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166">
         <v>7</v>
@@ -12145,13 +12145,13 @@
         <v>1</v>
       </c>
       <c r="S166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166">
         <v>7</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V166">
         <v>7</v>
@@ -12346,7 +12346,7 @@
         <v>7</v>
       </c>
       <c r="U169">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V169">
         <v>7</v>
@@ -12470,7 +12470,7 @@
         <v>1</v>
       </c>
       <c r="S171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171">
         <v>7</v>
@@ -12606,7 +12606,7 @@
         <v>7</v>
       </c>
       <c r="U173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V173">
         <v>7</v>
@@ -12671,7 +12671,7 @@
         <v>7</v>
       </c>
       <c r="U174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V174">
         <v>7</v>
@@ -12736,7 +12736,7 @@
         <v>7</v>
       </c>
       <c r="U175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V175">
         <v>7</v>
@@ -12795,7 +12795,7 @@
         <v>1</v>
       </c>
       <c r="S176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176">
         <v>7</v>
@@ -12931,7 +12931,7 @@
         <v>7</v>
       </c>
       <c r="U178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V178">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>7</v>
       </c>
       <c r="U179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V179">
         <v>7</v>
@@ -13061,7 +13061,7 @@
         <v>7</v>
       </c>
       <c r="U180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V180">
         <v>7</v>
@@ -13126,7 +13126,7 @@
         <v>7</v>
       </c>
       <c r="U181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V181">
         <v>7</v>
@@ -13256,7 +13256,7 @@
         <v>7</v>
       </c>
       <c r="U183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V183">
         <v>7</v>
@@ -13646,7 +13646,7 @@
         <v>7</v>
       </c>
       <c r="U189">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V189">
         <v>7</v>
@@ -13926,7 +13926,7 @@
         <v>25</v>
       </c>
       <c r="D194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>7</v>
@@ -13962,7 +13962,7 @@
         <v>1</v>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="b">
         <v>1</v>
@@ -14056,7 +14056,7 @@
         <v>25</v>
       </c>
       <c r="D196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196">
         <v>7</v>
@@ -14092,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="R196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S196" t="b">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         <v>6</v>
       </c>
       <c r="U196">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V196">
         <v>6</v>
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="U199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V199">
         <v>7</v>
@@ -14361,7 +14361,7 @@
         <v>7</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V200">
         <v>7</v>
@@ -14491,7 +14491,7 @@
         <v>7</v>
       </c>
       <c r="U202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V202">
         <v>7</v>
@@ -14511,7 +14511,7 @@
         <v>25</v>
       </c>
       <c r="D203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203">
         <v>7</v>
@@ -14550,13 +14550,13 @@
         <v>1</v>
       </c>
       <c r="S203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T203">
         <v>7</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V203">
         <v>7</v>
@@ -14881,7 +14881,7 @@
         <v>7</v>
       </c>
       <c r="U208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V208">
         <v>7</v>
@@ -15200,7 +15200,7 @@
         <v>1</v>
       </c>
       <c r="S213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T213">
         <v>7</v>
@@ -15265,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="S214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T214">
         <v>5</v>
@@ -15590,7 +15590,7 @@
         <v>1</v>
       </c>
       <c r="S219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T219">
         <v>7</v>
@@ -15791,7 +15791,7 @@
         <v>7</v>
       </c>
       <c r="U222">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V222">
         <v>7</v>
@@ -15856,7 +15856,7 @@
         <v>7</v>
       </c>
       <c r="U223">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="V223">
         <v>7</v>
@@ -15980,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="S225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T225">
         <v>7</v>
@@ -16181,7 +16181,7 @@
         <v>7</v>
       </c>
       <c r="U228">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V228">
         <v>7</v>
@@ -16266,7 +16266,7 @@
         <v>26</v>
       </c>
       <c r="D230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230">
         <v>7</v>
@@ -16305,13 +16305,13 @@
         <v>1</v>
       </c>
       <c r="S230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T230">
         <v>7</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V230">
         <v>7</v>
@@ -16435,7 +16435,7 @@
         <v>1</v>
       </c>
       <c r="S232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T232">
         <v>7</v>
@@ -16636,7 +16636,7 @@
         <v>7</v>
       </c>
       <c r="U235">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V235">
         <v>7</v>
@@ -16721,7 +16721,7 @@
         <v>27</v>
       </c>
       <c r="D237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>7</v>
@@ -16757,7 +16757,7 @@
         <v>1</v>
       </c>
       <c r="R237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S237" t="b">
         <v>1</v>
@@ -16766,7 +16766,7 @@
         <v>6</v>
       </c>
       <c r="U237">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V237">
         <v>6</v>
@@ -16786,7 +16786,7 @@
         <v>27</v>
       </c>
       <c r="D238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>7</v>
@@ -16822,7 +16822,7 @@
         <v>1</v>
       </c>
       <c r="R238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S238" t="b">
         <v>1</v>
@@ -16831,7 +16831,7 @@
         <v>7</v>
       </c>
       <c r="U238">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V238">
         <v>7</v>
@@ -16851,7 +16851,7 @@
         <v>27</v>
       </c>
       <c r="D239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>7</v>
@@ -16887,7 +16887,7 @@
         <v>1</v>
       </c>
       <c r="R239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S239" t="b">
         <v>1</v>
@@ -16896,7 +16896,7 @@
         <v>7</v>
       </c>
       <c r="U239">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V239">
         <v>7</v>
@@ -16916,7 +16916,7 @@
         <v>27</v>
       </c>
       <c r="D240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>7</v>
@@ -16952,7 +16952,7 @@
         <v>1</v>
       </c>
       <c r="R240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S240" t="b">
         <v>1</v>
@@ -16961,7 +16961,7 @@
         <v>6</v>
       </c>
       <c r="U240">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V240">
         <v>6</v>
@@ -17017,7 +17017,7 @@
         <v>0</v>
       </c>
       <c r="R241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S241" t="b">
         <v>0</v>
@@ -17147,10 +17147,10 @@
         <v>0</v>
       </c>
       <c r="R243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T243">
         <v>7</v>
@@ -17306,7 +17306,7 @@
         <v>27</v>
       </c>
       <c r="D246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246">
         <v>7</v>
@@ -17342,7 +17342,7 @@
         <v>1</v>
       </c>
       <c r="R246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S246" t="b">
         <v>1</v>
@@ -17351,7 +17351,7 @@
         <v>7</v>
       </c>
       <c r="U246">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V246">
         <v>7</v>
@@ -17472,10 +17472,10 @@
         <v>0</v>
       </c>
       <c r="R248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T248">
         <v>7</v>
@@ -17501,7 +17501,7 @@
         <v>27</v>
       </c>
       <c r="D249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>7</v>
@@ -17537,7 +17537,7 @@
         <v>1</v>
       </c>
       <c r="R249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S249" t="b">
         <v>1</v>
@@ -17546,7 +17546,7 @@
         <v>6</v>
       </c>
       <c r="U249">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V249">
         <v>6</v>
@@ -17605,7 +17605,7 @@
         <v>0</v>
       </c>
       <c r="S250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T250">
         <v>3</v>
@@ -17667,10 +17667,10 @@
         <v>0</v>
       </c>
       <c r="R251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T251">
         <v>7</v>
@@ -17806,7 +17806,7 @@
         <v>7</v>
       </c>
       <c r="U253">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V253">
         <v>7</v>
@@ -17865,7 +17865,7 @@
         <v>0</v>
       </c>
       <c r="S254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T254">
         <v>4</v>
@@ -18001,7 +18001,7 @@
         <v>7</v>
       </c>
       <c r="U256">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V256">
         <v>7</v>
@@ -18066,7 +18066,7 @@
         <v>7</v>
       </c>
       <c r="U257">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V257">
         <v>7</v>
@@ -18131,7 +18131,7 @@
         <v>7</v>
       </c>
       <c r="U258">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V258">
         <v>7</v>
@@ -18456,7 +18456,7 @@
         <v>7</v>
       </c>
       <c r="U263">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V263">
         <v>7</v>
@@ -18521,7 +18521,7 @@
         <v>7</v>
       </c>
       <c r="U264">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V264">
         <v>7</v>
@@ -18846,7 +18846,7 @@
         <v>7</v>
       </c>
       <c r="U269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V269">
         <v>7</v>
@@ -18866,7 +18866,7 @@
         <v>28</v>
       </c>
       <c r="D270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270">
         <v>7</v>
@@ -18905,13 +18905,13 @@
         <v>1</v>
       </c>
       <c r="S270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T270">
         <v>7</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V270">
         <v>7</v>
@@ -19041,7 +19041,7 @@
         <v>7</v>
       </c>
       <c r="U272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V272">
         <v>7</v>
@@ -19171,7 +19171,7 @@
         <v>7</v>
       </c>
       <c r="U274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V274">
         <v>7</v>
@@ -19236,7 +19236,7 @@
         <v>7</v>
       </c>
       <c r="U275">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V275">
         <v>7</v>
@@ -19295,7 +19295,7 @@
         <v>1</v>
       </c>
       <c r="S276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T276">
         <v>7</v>
@@ -19561,7 +19561,7 @@
         <v>7</v>
       </c>
       <c r="U280">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V280">
         <v>7</v>
@@ -19646,7 +19646,7 @@
         <v>28</v>
       </c>
       <c r="D282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E282">
         <v>7</v>
@@ -19685,13 +19685,13 @@
         <v>1</v>
       </c>
       <c r="S282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T282">
         <v>7</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V282">
         <v>7</v>
@@ -19756,7 +19756,7 @@
         <v>7</v>
       </c>
       <c r="U283">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V283">
         <v>7</v>
@@ -19821,7 +19821,7 @@
         <v>6</v>
       </c>
       <c r="U284">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V284">
         <v>6</v>
@@ -19886,7 +19886,7 @@
         <v>7</v>
       </c>
       <c r="U285">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V285">
         <v>7</v>
@@ -20276,7 +20276,7 @@
         <v>7</v>
       </c>
       <c r="U291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V291">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_ecoli.xlsx
@@ -88,10 +88,10 @@
     <t>cant_min_en_p_elegido</t>
   </si>
   <si>
-    <t>D35_R35_Pentropia</t>
+    <t>PRD35_PR35_CPent_UD080_PE45</t>
   </si>
   <si>
-    <t>D35_R35_Pproporcion</t>
+    <t>PRD35_PR35_CPprop_UD080_Ppp041</t>
   </si>
   <si>
     <t>im</t>
